--- a/output/促销组合优化建议.xlsx
+++ b/output/促销组合优化建议.xlsx
@@ -17,10 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -50,9 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,47 +440,32 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>开始日期</t>
+          <t>实际费用(元)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>结束日期</t>
+          <t>增量销售额(元)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>实际费用(元)</t>
+          <t>增量毛利(元)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>增量销售额(元)</t>
+          <t>ROI</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>增量毛利(元)</t>
+          <t>建议动作</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ROI</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>建议动作</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
           <t>关键依据</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>数据状态</t>
         </is>
       </c>
     </row>
@@ -501,45 +482,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>直播</t>
+          <t>会员日</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>46108</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>46121</v>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6741.41</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31053.33</v>
       </c>
       <c r="G2" t="n">
-        <v>20727.13</v>
+        <v>7263.43</v>
       </c>
       <c r="H2" t="n">
-        <v>55379.9</v>
-      </c>
-      <c r="I2" t="n">
-        <v>26844.63</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>调整优化</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>ROI 1.30(直播)</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.08</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,263.43元)/活动清单.实际费用(6,741.41元)</t>
         </is>
       </c>
     </row>
@@ -556,45 +526,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>节日促销</t>
+          <t>折扣</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46062</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>46065</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6968.65</v>
+      </c>
+      <c r="F3" t="n">
+        <v>57716.07</v>
       </c>
       <c r="G3" t="n">
-        <v>25269.43</v>
+        <v>10181.86</v>
       </c>
       <c r="H3" t="n">
-        <v>285203.03</v>
-      </c>
-      <c r="I3" t="n">
-        <v>79377.05</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>ROI 3.14(节日促销)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.46</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,181.86元)/活动清单.实际费用(6,968.65元)</t>
         </is>
       </c>
     </row>
@@ -611,45 +570,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>会员日</t>
+          <t>直播</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>46054</v>
+          <t>CH02</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6109.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17012.27</v>
       </c>
       <c r="G4" t="n">
-        <v>25800.26</v>
+        <v>3776.06</v>
       </c>
       <c r="H4" t="n">
-        <v>186741.02</v>
-      </c>
-      <c r="I4" t="n">
-        <v>61327.14</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>ROI 2.38(会员日)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.62</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(3,776.06元)/活动清单.实际费用(6,109.20元)</t>
         </is>
       </c>
     </row>
@@ -666,45 +614,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>节日促销</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CH02</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46165</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>46167</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6556.05</v>
+      </c>
+      <c r="F5" t="n">
+        <v>82140.50999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>14747.96</v>
+        <v>18875.98</v>
       </c>
       <c r="H5" t="n">
-        <v>293705.25</v>
-      </c>
-      <c r="I5" t="n">
-        <v>132709.65</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>ROI 9.00(折扣)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>2.88</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(18,875.98元)/活动清单.实际费用(6,556.05元)</t>
         </is>
       </c>
     </row>
@@ -721,7 +658,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>会员日</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -729,37 +666,26 @@
           <t>CH05</t>
         </is>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46125</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>46140</v>
+      <c r="E6" t="n">
+        <v>4640.84</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50269.8</v>
       </c>
       <c r="G6" t="n">
-        <v>31742.12</v>
+        <v>10686.85</v>
       </c>
       <c r="H6" t="n">
-        <v>23812.91</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8741.52</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>ROI 0.28(折扣)</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>2.3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,686.85元)/活动清单.实际费用(4,640.84元)</t>
         </is>
       </c>
     </row>
@@ -784,37 +710,26 @@
           <t>CH05</t>
         </is>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46033</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>46035</v>
+      <c r="E7" t="n">
+        <v>10630.78</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43619.43</v>
       </c>
       <c r="G7" t="n">
-        <v>15819.33</v>
+        <v>8347.43</v>
       </c>
       <c r="H7" t="n">
-        <v>148531.27</v>
-      </c>
-      <c r="I7" t="n">
-        <v>71417.75</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>ROI 4.51(满减)</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.79</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,347.43元)/活动清单.实际费用(10,630.78元)</t>
         </is>
       </c>
     </row>
@@ -831,45 +746,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>会员日</t>
+          <t>直播</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CH01</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46071</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>46086</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>14866.74</v>
+      </c>
+      <c r="F8" t="n">
+        <v>72093.45</v>
       </c>
       <c r="G8" t="n">
-        <v>25087.95</v>
+        <v>22055.01</v>
       </c>
       <c r="H8" t="n">
-        <v>224887.92</v>
-      </c>
-      <c r="I8" t="n">
-        <v>62689.25</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ROI 2.50(会员日)</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.48</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(22,055.01元)/活动清单.实际费用(14,866.74元)</t>
         </is>
       </c>
     </row>
@@ -891,40 +795,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>46207</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>7520.83</v>
+      </c>
+      <c r="F9" t="n">
+        <v>77054.13</v>
       </c>
       <c r="G9" t="n">
-        <v>26105.9</v>
+        <v>23079.3</v>
       </c>
       <c r="H9" t="n">
-        <v>27837.19</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6688.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>ROI 0.26(直播)</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>3.07</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(23,079.30元)/活动清单.实际费用(7,520.83元)</t>
         </is>
       </c>
     </row>
@@ -941,45 +834,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>节日促销</t>
+          <t>直播</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CH03</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46183</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>46191</v>
+          <t>CH05</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3337.67</v>
+      </c>
+      <c r="F10" t="n">
+        <v>17500.69</v>
       </c>
       <c r="G10" t="n">
-        <v>5891.91</v>
+        <v>3426.27</v>
       </c>
       <c r="H10" t="n">
-        <v>206118.99</v>
-      </c>
-      <c r="I10" t="n">
-        <v>102413.37</v>
-      </c>
-      <c r="J10" t="n">
-        <v>17.38</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>ROI 17.38(节日促销)</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.03</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(3,426.27元)/活动清单.实际费用(3,337.67元)</t>
         </is>
       </c>
     </row>
@@ -996,7 +878,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>节日促销</t>
+          <t>满减</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1004,37 +886,26 @@
           <t>CH05</t>
         </is>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46098</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>46110</v>
+      <c r="E11" t="n">
+        <v>5419.13</v>
+      </c>
+      <c r="F11" t="n">
+        <v>67143.09</v>
       </c>
       <c r="G11" t="n">
-        <v>20654.15</v>
+        <v>12857.97</v>
       </c>
       <c r="H11" t="n">
-        <v>38846.71</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10779.04</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>ROI 0.52(节日促销)</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>2.37</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,857.97元)/活动清单.实际费用(5,419.13元)</t>
         </is>
       </c>
     </row>
@@ -1051,45 +922,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>满减</t>
+          <t>直播</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46050</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>46054</v>
+          <t>CH01</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5952</v>
+      </c>
+      <c r="F12" t="n">
+        <v>52931.01</v>
       </c>
       <c r="G12" t="n">
-        <v>7882.81</v>
+        <v>12875.92</v>
       </c>
       <c r="H12" t="n">
-        <v>91964.49000000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>36214.49</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="K12" t="inlineStr">
+        <v>2.16</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>保留</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>ROI 4.59(满减)</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>已确认</t>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,875.92元)/活动清单.实际费用(5,952.00元)</t>
         </is>
       </c>
     </row>
@@ -1106,45 +966,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>节日促销</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CH02</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46148</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>46149</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4666.14</v>
+      </c>
+      <c r="F13" t="n">
+        <v>47656.08</v>
       </c>
       <c r="G13" t="n">
-        <v>19643.93</v>
+        <v>14994.62</v>
       </c>
       <c r="H13" t="n">
-        <v>103172.97</v>
-      </c>
-      <c r="I13" t="n">
-        <v>50683.74</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="K13" t="inlineStr">
+        <v>3.21</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>保留</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>ROI 2.58(折扣)</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>已确认</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(14,994.62元)/活动清单.实际费用(4,666.14元)</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1010,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>节日促销</t>
+          <t>会员日</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1169,37 +1018,26 @@
           <t>CH03</t>
         </is>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46096</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>46097</v>
+      <c r="E14" t="n">
+        <v>3457.45</v>
+      </c>
+      <c r="F14" t="n">
+        <v>63164.86</v>
       </c>
       <c r="G14" t="n">
-        <v>12203.59</v>
+        <v>15512.3</v>
       </c>
       <c r="H14" t="n">
-        <v>75102</v>
-      </c>
-      <c r="I14" t="n">
-        <v>17346.36</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>调整优化</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>ROI 1.42(节日促销)</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>4.49</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(15,512.30元)/活动清单.实际费用(3,457.45元)</t>
         </is>
       </c>
     </row>
@@ -1216,45 +1054,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>节日促销</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CH06</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46052</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>46060</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6394.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>65103.22</v>
       </c>
       <c r="G15" t="n">
-        <v>21858.09</v>
+        <v>14779.31</v>
       </c>
       <c r="H15" t="n">
-        <v>201065.6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>60013.89</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K15" t="inlineStr">
+        <v>2.31</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>保留</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>ROI 2.75(折扣)</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>已确认</t>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(14,779.31元)/活动清单.实际费用(6,394.80元)</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1098,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>节日促销</t>
+          <t>直播</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1279,37 +1106,26 @@
           <t>CH03</t>
         </is>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46202</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>46203</v>
+      <c r="E16" t="n">
+        <v>9459.969999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>118376.98</v>
       </c>
       <c r="G16" t="n">
-        <v>2577.31</v>
+        <v>20555.26</v>
       </c>
       <c r="H16" t="n">
-        <v>94615.17999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>28256.97</v>
-      </c>
-      <c r="J16" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>ROI 10.96(节日促销)</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>2.17</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(20,555.26元)/活动清单.实际费用(9,459.97元)</t>
         </is>
       </c>
     </row>
@@ -1326,45 +1142,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>会员日</t>
+          <t>直播</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CH01</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46109</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>46121</v>
+          <t>CH05</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5785.99</v>
+      </c>
+      <c r="F17" t="n">
+        <v>65970.73</v>
       </c>
       <c r="G17" t="n">
-        <v>14059.35</v>
+        <v>16955.27</v>
       </c>
       <c r="H17" t="n">
-        <v>102590.25</v>
-      </c>
-      <c r="I17" t="n">
-        <v>26913.95</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>调整优化</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>ROI 1.91(会员日)</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>2.93</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(16,955.27元)/活动清单.实际费用(5,785.99元)</t>
         </is>
       </c>
     </row>
@@ -1381,45 +1186,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>直播</t>
+          <t>折扣</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46167</v>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>46177</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>14112.84</v>
+      </c>
+      <c r="F18" t="n">
+        <v>38056.68</v>
       </c>
       <c r="G18" t="n">
-        <v>18376.94</v>
+        <v>9240.82</v>
       </c>
       <c r="H18" t="n">
-        <v>56619.75</v>
-      </c>
-      <c r="I18" t="n">
-        <v>13137.48</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>ROI 0.71(直播)</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.65</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(9,240.82元)/活动清单.实际费用(14,112.84元)</t>
         </is>
       </c>
     </row>
@@ -1436,45 +1230,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>直播</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CH01</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>46153</v>
+          <t>CH05</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>11836.73</v>
+      </c>
+      <c r="F19" t="n">
+        <v>58911.05</v>
       </c>
       <c r="G19" t="n">
-        <v>26399.52</v>
+        <v>20411.2</v>
       </c>
       <c r="H19" t="n">
-        <v>30656.91</v>
-      </c>
-      <c r="I19" t="n">
-        <v>10036.84</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>ROI 0.38(折扣)</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.72</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(20,411.20元)/活动清单.实际费用(11,836.73元)</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1274,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>满减</t>
+          <t>节日促销</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1499,37 +1282,26 @@
           <t>CH05</t>
         </is>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46023</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>46032</v>
+      <c r="E20" t="n">
+        <v>2772.57</v>
+      </c>
+      <c r="F20" t="n">
+        <v>23732.33</v>
       </c>
       <c r="G20" t="n">
-        <v>26258.05</v>
+        <v>5337.47</v>
       </c>
       <c r="H20" t="n">
-        <v>124511.12</v>
-      </c>
-      <c r="I20" t="n">
-        <v>41916.25</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>调整优化</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>ROI 1.60(满减)</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.93</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,337.47元)/活动清单.实际费用(2,772.57元)</t>
         </is>
       </c>
     </row>
@@ -1546,45 +1318,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>会员日</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CH03</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>46173</v>
+          <t>CH05</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>9135.48</v>
+      </c>
+      <c r="F21" t="n">
+        <v>69471.31</v>
       </c>
       <c r="G21" t="n">
-        <v>24443.11</v>
+        <v>15353.97</v>
       </c>
       <c r="H21" t="n">
-        <v>135659.21</v>
-      </c>
-      <c r="I21" t="n">
-        <v>57193.72</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>ROI 2.34(折扣)</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.68</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(15,353.97元)/活动清单.实际费用(9,135.48元)</t>
         </is>
       </c>
     </row>
@@ -1601,45 +1362,34 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>直播</t>
+          <t>会员日</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CH03</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46114</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>46117</v>
+          <t>CH06</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3562.82</v>
+      </c>
+      <c r="F22" t="n">
+        <v>10113.4</v>
       </c>
       <c r="G22" t="n">
-        <v>22801.53</v>
+        <v>2159.61</v>
       </c>
       <c r="H22" t="n">
-        <v>23802.06</v>
-      </c>
-      <c r="I22" t="n">
-        <v>6465.03</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>ROI 0.28(直播)</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.61</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(2,159.61元)/活动清单.实际费用(3,562.82元)</t>
         </is>
       </c>
     </row>
@@ -1656,45 +1406,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>直播</t>
+          <t>满减</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>46138</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>12365.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>100032.32</v>
       </c>
       <c r="G23" t="n">
-        <v>29471.23</v>
+        <v>18609.9</v>
       </c>
       <c r="H23" t="n">
-        <v>183512.75</v>
-      </c>
-      <c r="I23" t="n">
-        <v>77788.61</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>ROI 2.64(直播)</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.5</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(18,609.90元)/活动清单.实际费用(12,365.50元)</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1450,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>会员日</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1719,37 +1458,26 @@
           <t>CH03</t>
         </is>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46052</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>46061</v>
+      <c r="E24" t="n">
+        <v>5533.43</v>
+      </c>
+      <c r="F24" t="n">
+        <v>103987.94</v>
       </c>
       <c r="G24" t="n">
-        <v>12868.87</v>
+        <v>21035.4</v>
       </c>
       <c r="H24" t="n">
-        <v>325633.15</v>
-      </c>
-      <c r="I24" t="n">
-        <v>80548.53</v>
-      </c>
-      <c r="J24" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>ROI 6.26(折扣)</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>3.8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(21,035.40元)/活动清单.实际费用(5,533.43元)</t>
         </is>
       </c>
     </row>
@@ -1774,37 +1502,26 @@
           <t>CH05</t>
         </is>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46118</v>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>46121</v>
+      <c r="E25" t="n">
+        <v>11915.11</v>
+      </c>
+      <c r="F25" t="n">
+        <v>48203.7</v>
       </c>
       <c r="G25" t="n">
-        <v>11979.03</v>
+        <v>10723.09</v>
       </c>
       <c r="H25" t="n">
-        <v>239311.7</v>
-      </c>
-      <c r="I25" t="n">
-        <v>89250.24000000001</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>ROI 7.45(满减)</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.9</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,723.09元)/活动清单.实际费用(11,915.11元)</t>
         </is>
       </c>
     </row>
@@ -1821,45 +1538,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>节日促销</t>
+          <t>会员日</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CH04</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>46193</v>
+          <t>CH05</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>7472.4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>61560.37</v>
       </c>
       <c r="G26" t="n">
-        <v>31275.26</v>
+        <v>18574.61</v>
       </c>
       <c r="H26" t="n">
-        <v>40812.29</v>
-      </c>
-      <c r="I26" t="n">
-        <v>8559.25</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>ROI 0.27(节日促销)</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>2.49</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(18,574.61元)/活动清单.实际费用(7,472.40元)</t>
         </is>
       </c>
     </row>
@@ -1876,45 +1582,34 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>会员日</t>
+          <t>满减</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CH06</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>46075</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4473.51</v>
+      </c>
+      <c r="F27" t="n">
+        <v>77435.14</v>
       </c>
       <c r="G27" t="n">
-        <v>24372.53</v>
+        <v>12849.12</v>
       </c>
       <c r="H27" t="n">
-        <v>104457.72</v>
-      </c>
-      <c r="I27" t="n">
-        <v>22540.23</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>ROI 0.92(会员日)</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>2.87</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,849.12元)/活动清单.实际费用(4,473.51元)</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1626,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>节日促销</t>
+          <t>折扣</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1939,37 +1634,26 @@
           <t>CH05</t>
         </is>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46068</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>46081</v>
+      <c r="E28" t="n">
+        <v>11073.64</v>
+      </c>
+      <c r="F28" t="n">
+        <v>29592.1</v>
       </c>
       <c r="G28" t="n">
-        <v>7458.5</v>
+        <v>6346.7</v>
       </c>
       <c r="H28" t="n">
-        <v>227791.92</v>
-      </c>
-      <c r="I28" t="n">
-        <v>100376.27</v>
-      </c>
-      <c r="J28" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>ROI 13.46(节日促销)</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.57</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(6,346.70元)/活动清单.实际费用(11,073.64元)</t>
         </is>
       </c>
     </row>
@@ -1986,45 +1670,34 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>会员日</t>
+          <t>节日促销</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CH01</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>46154</v>
+          <t>CH05</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3594.29</v>
+      </c>
+      <c r="F29" t="n">
+        <v>29029.79</v>
       </c>
       <c r="G29" t="n">
-        <v>6071.97</v>
+        <v>7417.48</v>
       </c>
       <c r="H29" t="n">
-        <v>21232.21</v>
-      </c>
-      <c r="I29" t="n">
-        <v>5776.36</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>ROI 0.95(会员日)</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>2.06</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,417.48元)/活动清单.实际费用(3,594.29元)</t>
         </is>
       </c>
     </row>
@@ -2041,45 +1714,34 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>会员日</t>
+          <t>节日促销</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CH02</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>46135</v>
+          <t>CH01</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5634.01</v>
+      </c>
+      <c r="F30" t="n">
+        <v>33794.86</v>
       </c>
       <c r="G30" t="n">
-        <v>2929.29</v>
+        <v>5849.08</v>
       </c>
       <c r="H30" t="n">
-        <v>120626.73</v>
-      </c>
-      <c r="I30" t="n">
-        <v>56820.62</v>
-      </c>
-      <c r="J30" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>ROI 19.40(会员日)</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.04</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,849.08元)/活动清单.实际费用(5,634.01元)</t>
         </is>
       </c>
     </row>
@@ -2096,45 +1758,34 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>会员日</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CH04</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46141</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>46144</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>14470.09</v>
+      </c>
+      <c r="F31" t="n">
+        <v>92118.34</v>
       </c>
       <c r="G31" t="n">
-        <v>7886.21</v>
+        <v>19015.88</v>
       </c>
       <c r="H31" t="n">
-        <v>240706.04</v>
-      </c>
-      <c r="I31" t="n">
-        <v>64037.67</v>
-      </c>
-      <c r="J31" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>ROI 8.12(折扣)</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.31</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(19,015.88元)/活动清单.实际费用(14,470.09元)</t>
         </is>
       </c>
     </row>
@@ -2159,37 +1810,26 @@
           <t>CH06</t>
         </is>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>46150</v>
+      <c r="E32" t="n">
+        <v>15528.58</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9187.42</v>
       </c>
       <c r="G32" t="n">
-        <v>19486.29</v>
+        <v>2060.09</v>
       </c>
       <c r="H32" t="n">
-        <v>194352.15</v>
-      </c>
-      <c r="I32" t="n">
-        <v>84981.8</v>
-      </c>
-      <c r="J32" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>ROI 4.36(会员日)</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.13</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(2,060.09元)/活动清单.实际费用(15,528.58元)</t>
         </is>
       </c>
     </row>
@@ -2211,40 +1851,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46053</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>46055</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>13945.12</v>
+      </c>
+      <c r="F33" t="n">
+        <v>62844.73</v>
       </c>
       <c r="G33" t="n">
-        <v>16886.6</v>
+        <v>16447.27</v>
       </c>
       <c r="H33" t="n">
-        <v>124305.69</v>
-      </c>
-      <c r="I33" t="n">
-        <v>35238.34</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>ROI 2.09(满减)</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.18</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(16,447.27元)/活动清单.实际费用(13,945.12元)</t>
         </is>
       </c>
     </row>
@@ -2261,45 +1890,34 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>会员日</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>46086</v>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>11896.7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>51697.07</v>
       </c>
       <c r="G34" t="n">
-        <v>1900.42</v>
+        <v>10837.62</v>
       </c>
       <c r="H34" t="n">
-        <v>176844.17</v>
-      </c>
-      <c r="I34" t="n">
-        <v>40529.28</v>
-      </c>
-      <c r="J34" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>ROI 21.33(折扣)</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.91</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,837.62元)/活动清单.实际费用(11,896.70元)</t>
         </is>
       </c>
     </row>
@@ -2321,40 +1939,29 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46073</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>46086</v>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2890.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>66397.72</v>
       </c>
       <c r="G35" t="n">
-        <v>23281.09</v>
+        <v>17579.98</v>
       </c>
       <c r="H35" t="n">
-        <v>158330.36</v>
-      </c>
-      <c r="I35" t="n">
-        <v>39923.63</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>调整优化</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>ROI 1.71(满减)</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>6.08</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(17,579.98元)/活动清单.实际费用(2,890.20元)</t>
         </is>
       </c>
     </row>
@@ -2371,7 +1978,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>满减</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2379,37 +1986,26 @@
           <t>CH03</t>
         </is>
       </c>
-      <c r="E36" s="1" t="n">
-        <v>46024</v>
-      </c>
-      <c r="F36" s="1" t="n">
-        <v>46025</v>
+      <c r="E36" t="n">
+        <v>3470.91</v>
+      </c>
+      <c r="F36" t="n">
+        <v>52765.84</v>
       </c>
       <c r="G36" t="n">
-        <v>5014.19</v>
+        <v>10511.97</v>
       </c>
       <c r="H36" t="n">
-        <v>194955.95</v>
-      </c>
-      <c r="I36" t="n">
-        <v>42250.69</v>
-      </c>
-      <c r="J36" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>ROI 8.43(折扣)</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>3.03</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,511.97元)/活动清单.实际费用(3,470.91元)</t>
         </is>
       </c>
     </row>
@@ -2426,45 +2022,34 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>节日促销</t>
+          <t>直播</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>46139</v>
-      </c>
-      <c r="F37" s="1" t="n">
-        <v>46153</v>
+          <t>CH01</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>11327.73</v>
+      </c>
+      <c r="F37" t="n">
+        <v>18315.89</v>
       </c>
       <c r="G37" t="n">
-        <v>10657.6</v>
+        <v>4552.04</v>
       </c>
       <c r="H37" t="n">
-        <v>262271.61</v>
-      </c>
-      <c r="I37" t="n">
-        <v>104475.87</v>
-      </c>
-      <c r="J37" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>ROI 9.80(节日促销)</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.4</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,552.04元)/活动清单.实际费用(11,327.73元)</t>
         </is>
       </c>
     </row>
@@ -2481,45 +2066,34 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>会员日</t>
+          <t>折扣</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CH02</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>46110</v>
-      </c>
-      <c r="F38" s="1" t="n">
-        <v>46119</v>
+          <t>CH05</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>8975.139999999999</v>
+      </c>
+      <c r="F38" t="n">
+        <v>58272.9</v>
       </c>
       <c r="G38" t="n">
-        <v>3156.14</v>
+        <v>13616.56</v>
       </c>
       <c r="H38" t="n">
-        <v>103974.79</v>
-      </c>
-      <c r="I38" t="n">
-        <v>43025.08</v>
-      </c>
-      <c r="J38" t="n">
-        <v>13.63</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>ROI 13.63(会员日)</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.52</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(13,616.56元)/活动清单.实际费用(8,975.14元)</t>
         </is>
       </c>
     </row>
@@ -2536,45 +2110,34 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>会员日</t>
+          <t>满减</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CH02</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>46118</v>
-      </c>
-      <c r="F39" s="1" t="n">
-        <v>46120</v>
+          <t>CH01</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>10473.02</v>
+      </c>
+      <c r="F39" t="n">
+        <v>29277.41</v>
       </c>
       <c r="G39" t="n">
-        <v>17346.47</v>
+        <v>8630.52</v>
       </c>
       <c r="H39" t="n">
-        <v>187632.62</v>
-      </c>
-      <c r="I39" t="n">
-        <v>63526.75</v>
-      </c>
-      <c r="J39" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>ROI 3.66(会员日)</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.82</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,630.52元)/活动清单.实际费用(10,473.02元)</t>
         </is>
       </c>
     </row>
@@ -2596,40 +2159,29 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CH03</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>46193</v>
-      </c>
-      <c r="F40" s="1" t="n">
-        <v>46208</v>
+          <t>CH05</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4381.95</v>
+      </c>
+      <c r="F40" t="n">
+        <v>69534.55</v>
       </c>
       <c r="G40" t="n">
-        <v>3093.79</v>
+        <v>18424.66</v>
       </c>
       <c r="H40" t="n">
-        <v>141291.71</v>
-      </c>
-      <c r="I40" t="n">
-        <v>61832.52</v>
-      </c>
-      <c r="J40" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>ROI 19.99(节日促销)</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>4.2</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(18,424.66元)/活动清单.实际费用(4,381.95元)</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2198,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>会员日</t>
+          <t>折扣</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2654,37 +2206,26 @@
           <t>CH03</t>
         </is>
       </c>
-      <c r="E41" s="1" t="n">
-        <v>46186</v>
-      </c>
-      <c r="F41" s="1" t="n">
-        <v>46199</v>
+      <c r="E41" t="n">
+        <v>4119.28</v>
+      </c>
+      <c r="F41" t="n">
+        <v>69126.8</v>
       </c>
       <c r="G41" t="n">
-        <v>19976.44</v>
+        <v>12085.1</v>
       </c>
       <c r="H41" t="n">
-        <v>27700.89</v>
-      </c>
-      <c r="I41" t="n">
-        <v>7618.57</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>ROI 0.38(会员日)</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>2.93</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,085.10元)/活动清单.实际费用(4,119.28元)</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2242,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>会员日</t>
+          <t>满减</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2709,37 +2250,26 @@
           <t>CH05</t>
         </is>
       </c>
-      <c r="E42" s="1" t="n">
-        <v>46116</v>
-      </c>
-      <c r="F42" s="1" t="n">
-        <v>46129</v>
+      <c r="E42" t="n">
+        <v>2110.03</v>
+      </c>
+      <c r="F42" t="n">
+        <v>56140.97</v>
       </c>
       <c r="G42" t="n">
-        <v>6355.07</v>
+        <v>12012.59</v>
       </c>
       <c r="H42" t="n">
-        <v>275500.8</v>
-      </c>
-      <c r="I42" t="n">
-        <v>115314.33</v>
-      </c>
-      <c r="J42" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>ROI 18.15(会员日)</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>5.69</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,012.59元)/活动清单.实际费用(2,110.03元)</t>
         </is>
       </c>
     </row>
@@ -2756,45 +2286,34 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>节日促销</t>
+          <t>满减</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="F43" s="1" t="n">
-        <v>46072</v>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>11099.07</v>
+      </c>
+      <c r="F43" t="n">
+        <v>47517.01</v>
       </c>
       <c r="G43" t="n">
-        <v>24991.64</v>
+        <v>10717.52</v>
       </c>
       <c r="H43" t="n">
-        <v>84183.53999999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>26225.91</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>调整优化</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>ROI 1.05(节日促销)</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.97</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,717.52元)/活动清单.实际费用(11,099.07元)</t>
         </is>
       </c>
     </row>
@@ -2811,45 +2330,34 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>直播</t>
+          <t>会员日</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>46148</v>
-      </c>
-      <c r="F44" s="1" t="n">
-        <v>46160</v>
+          <t>CH04</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>14244.19</v>
+      </c>
+      <c r="F44" t="n">
+        <v>31001.77</v>
       </c>
       <c r="G44" t="n">
-        <v>10344.3</v>
+        <v>6119.49</v>
       </c>
       <c r="H44" t="n">
-        <v>269943.8</v>
-      </c>
-      <c r="I44" t="n">
-        <v>114288.87</v>
-      </c>
-      <c r="J44" t="n">
-        <v>11.05</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>ROI 11.05(直播)</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.43</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(6,119.49元)/活动清单.实际费用(14,244.19元)</t>
         </is>
       </c>
     </row>
@@ -2871,40 +2379,29 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CH03</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46089</v>
-      </c>
-      <c r="F45" s="1" t="n">
-        <v>46096</v>
+          <t>CH02</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>12714.32</v>
+      </c>
+      <c r="F45" t="n">
+        <v>14419.92</v>
       </c>
       <c r="G45" t="n">
-        <v>11055.94</v>
+        <v>2148.36</v>
       </c>
       <c r="H45" t="n">
-        <v>25279</v>
-      </c>
-      <c r="I45" t="n">
-        <v>7827.36</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>ROI 0.71(直播)</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.17</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(2,148.36元)/活动清单.实际费用(12,714.32元)</t>
         </is>
       </c>
     </row>
@@ -2921,45 +2418,34 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>满减</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CH03</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46110</v>
-      </c>
-      <c r="F46" s="1" t="n">
-        <v>46111</v>
+          <t>CH05</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>14090.22</v>
+      </c>
+      <c r="F46" t="n">
+        <v>34575.88</v>
       </c>
       <c r="G46" t="n">
-        <v>17423.6</v>
+        <v>6639.58</v>
       </c>
       <c r="H46" t="n">
-        <v>191062.7</v>
-      </c>
-      <c r="I46" t="n">
-        <v>81939.7</v>
-      </c>
-      <c r="J46" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>ROI 4.70(折扣)</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.47</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(6,639.58元)/活动清单.实际费用(14,090.22元)</t>
         </is>
       </c>
     </row>
@@ -2976,45 +2462,34 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>节日促销</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46146</v>
-      </c>
-      <c r="F47" s="1" t="n">
-        <v>46151</v>
+          <t>CH03</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6567.16</v>
+      </c>
+      <c r="F47" t="n">
+        <v>68031.12</v>
       </c>
       <c r="G47" t="n">
-        <v>29649.63</v>
+        <v>11637.05</v>
       </c>
       <c r="H47" t="n">
-        <v>309444.12</v>
-      </c>
-      <c r="I47" t="n">
-        <v>127615.75</v>
-      </c>
-      <c r="J47" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>ROI 4.30(折扣)</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>1.77</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>调整</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,637.05元)/活动清单.实际费用(6,567.16元)</t>
         </is>
       </c>
     </row>
@@ -3036,40 +2511,29 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="n">
-        <v>46047</v>
-      </c>
-      <c r="F48" s="1" t="n">
-        <v>46060</v>
+          <t>CH01</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>11791.47</v>
+      </c>
+      <c r="F48" t="n">
+        <v>25553.34</v>
       </c>
       <c r="G48" t="n">
-        <v>17491.8</v>
+        <v>6082.83</v>
       </c>
       <c r="H48" t="n">
-        <v>209431.77</v>
-      </c>
-      <c r="I48" t="n">
-        <v>48682.7</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>保留</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>ROI 2.78(会员日)</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.52</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(6,082.83元)/活动清单.实际费用(11,791.47元)</t>
         </is>
       </c>
     </row>
@@ -3086,7 +2550,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>折扣</t>
+          <t>会员日</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3094,37 +2558,26 @@
           <t>CH01</t>
         </is>
       </c>
-      <c r="E49" s="1" t="n">
-        <v>46073</v>
-      </c>
-      <c r="F49" s="1" t="n">
-        <v>46086</v>
+      <c r="E49" t="n">
+        <v>13348.43</v>
+      </c>
+      <c r="F49" t="n">
+        <v>40545.47</v>
       </c>
       <c r="G49" t="n">
-        <v>15334.08</v>
+        <v>9090.17</v>
       </c>
       <c r="H49" t="n">
-        <v>56538.18</v>
-      </c>
-      <c r="I49" t="n">
-        <v>19267.69</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>调整优化</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>ROI 1.26(折扣)</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.68</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(9,090.17元)/活动清单.实际费用(13,348.43元)</t>
         </is>
       </c>
     </row>
@@ -3141,45 +2594,34 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>会员日</t>
+          <t>折扣</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CH05</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="n">
-        <v>46169</v>
-      </c>
-      <c r="F50" s="1" t="n">
-        <v>46179</v>
+          <t>CH01</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3888.45</v>
+      </c>
+      <c r="F50" t="n">
+        <v>15314.82</v>
       </c>
       <c r="G50" t="n">
-        <v>5417.89</v>
+        <v>3112.38</v>
       </c>
       <c r="H50" t="n">
-        <v>136833.75</v>
-      </c>
-      <c r="I50" t="n">
-        <v>55192.7</v>
-      </c>
-      <c r="J50" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>保留并加大投入</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>ROI 10.19(会员日)</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>0.8</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(3,112.38元)/活动清单.实际费用(3,888.45元)</t>
         </is>
       </c>
     </row>
@@ -3196,7 +2638,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>直播</t>
+          <t>折扣</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3204,37 +2646,26 @@
           <t>CH03</t>
         </is>
       </c>
-      <c r="E51" s="1" t="n">
-        <v>46171</v>
-      </c>
-      <c r="F51" s="1" t="n">
-        <v>46180</v>
+      <c r="E51" t="n">
+        <v>12873.49</v>
+      </c>
+      <c r="F51" t="n">
+        <v>118190.11</v>
       </c>
       <c r="G51" t="n">
-        <v>27824.74</v>
+        <v>28883.19</v>
       </c>
       <c r="H51" t="n">
-        <v>95892.36</v>
-      </c>
-      <c r="I51" t="n">
-        <v>26811.58</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>取消/收缩</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>ROI 0.96(直播)</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>已确认</t>
+        <v>2.24</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(28,883.19元)/活动清单.实际费用(12,873.49元)</t>
         </is>
       </c>
     </row>
@@ -3282,17 +2713,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>会员日 + 小型满减</t>
+          <t>会员日 + 满减(淡季稳定流量)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>80,000 - 120,000</t>
+          <t>49,943.46 - 66,591.28</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>暑期消费</t>
+          <t>暑期消费/暑促</t>
         </is>
       </c>
     </row>
@@ -3309,7 +2740,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>60,000 - 100,000</t>
+          <t>41,619.55 - 58,267.37</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3326,12 +2757,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>品类联合促销</t>
+          <t>折扣 + 品类联合促销</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>100,000 - 150,000</t>
+          <t>58,267.37 - 74,915.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3348,17 +2779,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>国庆大促 + 直播</t>
+          <t>节日促销(国庆) + 满减</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>200,000 - 300,000</t>
+          <t>66,591.28 - 83,239.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>国庆</t>
+          <t>国庆黄金周</t>
         </is>
       </c>
     </row>
@@ -3370,12 +2801,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>双 11 大促</t>
+          <t>折扣 + 节日促销(双 11)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>500,000 - 800,000</t>
+          <t>91,563.02 - 108,210.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3392,17 +2823,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>双 12 + 年货节</t>
+          <t>满减 + 节日促销(双 12/年货节)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>300,000 - 500,000</t>
+          <t>74,915.20 - 91,563.02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>年终</t>
+          <t>双 12/年货节</t>
         </is>
       </c>
     </row>

--- a/output/促销组合优化建议.xlsx
+++ b/output/促销组合优化建议.xlsx
@@ -494,13 +494,13 @@
         <v>6741.41</v>
       </c>
       <c r="F2" t="n">
-        <v>31053.33</v>
+        <v>50075.15</v>
       </c>
       <c r="G2" t="n">
-        <v>7263.43</v>
+        <v>11593.91</v>
       </c>
       <c r="H2" t="n">
-        <v>1.08</v>
+        <v>1.72</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,263.43元)/活动清单.实际费用(6,741.41元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,593.91元)/活动清单.实际费用(6,741.41元)</t>
         </is>
       </c>
     </row>
@@ -538,22 +538,22 @@
         <v>6968.65</v>
       </c>
       <c r="F3" t="n">
-        <v>57716.07</v>
+        <v>19134.41</v>
       </c>
       <c r="G3" t="n">
-        <v>10181.86</v>
+        <v>4754.44</v>
       </c>
       <c r="H3" t="n">
-        <v>1.46</v>
+        <v>0.68</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,181.86元)/活动清单.实际费用(6,968.65元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,754.44元)/活动清单.实际费用(6,968.65元)</t>
         </is>
       </c>
     </row>
@@ -582,22 +582,22 @@
         <v>6109.2</v>
       </c>
       <c r="F4" t="n">
-        <v>17012.27</v>
+        <v>68982.35000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>3776.06</v>
+        <v>16465.53</v>
       </c>
       <c r="H4" t="n">
-        <v>0.62</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(3,776.06元)/活动清单.实际费用(6,109.20元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(16,465.53元)/活动清单.实际费用(6,109.20元)</t>
         </is>
       </c>
     </row>
@@ -626,22 +626,22 @@
         <v>6556.05</v>
       </c>
       <c r="F5" t="n">
-        <v>82140.50999999999</v>
+        <v>28442.81</v>
       </c>
       <c r="G5" t="n">
-        <v>18875.98</v>
+        <v>8358.969999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>2.88</v>
+        <v>1.28</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(18,875.98元)/活动清单.实际费用(6,556.05元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,358.97元)/活动清单.实际费用(6,556.05元)</t>
         </is>
       </c>
     </row>
@@ -670,13 +670,13 @@
         <v>4640.84</v>
       </c>
       <c r="F6" t="n">
-        <v>50269.8</v>
+        <v>41693.1</v>
       </c>
       <c r="G6" t="n">
-        <v>10686.85</v>
+        <v>11181.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,686.85元)/活动清单.实际费用(4,640.84元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,181.90元)/活动清单.实际费用(4,640.84元)</t>
         </is>
       </c>
     </row>
@@ -714,13 +714,13 @@
         <v>10630.78</v>
       </c>
       <c r="F7" t="n">
-        <v>43619.43</v>
+        <v>34361.06</v>
       </c>
       <c r="G7" t="n">
-        <v>8347.43</v>
+        <v>7973.69</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,347.43元)/活动清单.实际费用(10,630.78元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,973.69元)/活动清单.实际费用(10,630.78元)</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
         <v>14866.74</v>
       </c>
       <c r="F8" t="n">
-        <v>72093.45</v>
+        <v>19248.13</v>
       </c>
       <c r="G8" t="n">
-        <v>22055.01</v>
+        <v>5097.34</v>
       </c>
       <c r="H8" t="n">
-        <v>1.48</v>
+        <v>0.34</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(22,055.01元)/活动清单.实际费用(14,866.74元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,097.34元)/活动清单.实际费用(14,866.74元)</t>
         </is>
       </c>
     </row>
@@ -802,13 +802,13 @@
         <v>7520.83</v>
       </c>
       <c r="F9" t="n">
-        <v>77054.13</v>
+        <v>58493.62</v>
       </c>
       <c r="G9" t="n">
-        <v>23079.3</v>
+        <v>15250.31</v>
       </c>
       <c r="H9" t="n">
-        <v>3.07</v>
+        <v>2.03</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(23,079.30元)/活动清单.实际费用(7,520.83元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(15,250.31元)/活动清单.实际费用(7,520.83元)</t>
         </is>
       </c>
     </row>
@@ -846,22 +846,22 @@
         <v>3337.67</v>
       </c>
       <c r="F10" t="n">
-        <v>17500.69</v>
+        <v>36035.24</v>
       </c>
       <c r="G10" t="n">
-        <v>3426.27</v>
+        <v>8845.559999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.03</v>
+        <v>2.65</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(3,426.27元)/活动清单.实际费用(3,337.67元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,845.56元)/活动清单.实际费用(3,337.67元)</t>
         </is>
       </c>
     </row>
@@ -890,13 +890,13 @@
         <v>5419.13</v>
       </c>
       <c r="F11" t="n">
-        <v>67143.09</v>
+        <v>46641.14</v>
       </c>
       <c r="G11" t="n">
-        <v>12857.97</v>
+        <v>12352.85</v>
       </c>
       <c r="H11" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,857.97元)/活动清单.实际费用(5,419.13元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,352.85元)/活动清单.实际费用(5,419.13元)</t>
         </is>
       </c>
     </row>
@@ -934,22 +934,22 @@
         <v>5952</v>
       </c>
       <c r="F12" t="n">
-        <v>52931.01</v>
+        <v>29446.19</v>
       </c>
       <c r="G12" t="n">
-        <v>12875.92</v>
+        <v>7516.62</v>
       </c>
       <c r="H12" t="n">
-        <v>2.16</v>
+        <v>1.26</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,875.92元)/活动清单.实际费用(5,952.00元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,516.62元)/活动清单.实际费用(5,952.00元)</t>
         </is>
       </c>
     </row>
@@ -978,22 +978,22 @@
         <v>4666.14</v>
       </c>
       <c r="F13" t="n">
-        <v>47656.08</v>
+        <v>14785.91</v>
       </c>
       <c r="G13" t="n">
-        <v>14994.62</v>
+        <v>3411.63</v>
       </c>
       <c r="H13" t="n">
-        <v>3.21</v>
+        <v>0.73</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(14,994.62元)/活动清单.实际费用(4,666.14元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(3,411.63元)/活动清单.实际费用(4,666.14元)</t>
         </is>
       </c>
     </row>
@@ -1022,22 +1022,22 @@
         <v>3457.45</v>
       </c>
       <c r="F14" t="n">
-        <v>63164.86</v>
+        <v>18565.57</v>
       </c>
       <c r="G14" t="n">
-        <v>15512.3</v>
+        <v>4465.44</v>
       </c>
       <c r="H14" t="n">
-        <v>4.49</v>
+        <v>1.29</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(15,512.30元)/活动清单.实际费用(3,457.45元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,465.44元)/活动清单.实际费用(3,457.45元)</t>
         </is>
       </c>
     </row>
@@ -1066,13 +1066,13 @@
         <v>6394.8</v>
       </c>
       <c r="F15" t="n">
-        <v>65103.22</v>
+        <v>54941.95</v>
       </c>
       <c r="G15" t="n">
-        <v>14779.31</v>
+        <v>13178.84</v>
       </c>
       <c r="H15" t="n">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(14,779.31元)/活动清单.实际费用(6,394.80元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(13,178.84元)/活动清单.实际费用(6,394.80元)</t>
         </is>
       </c>
     </row>
@@ -1110,13 +1110,13 @@
         <v>9459.969999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>118376.98</v>
+        <v>104957.04</v>
       </c>
       <c r="G16" t="n">
-        <v>20555.26</v>
+        <v>27043.37</v>
       </c>
       <c r="H16" t="n">
-        <v>2.17</v>
+        <v>2.86</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(20,555.26元)/活动清单.实际费用(9,459.97元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(27,043.37元)/活动清单.实际费用(9,459.97元)</t>
         </is>
       </c>
     </row>
@@ -1154,22 +1154,22 @@
         <v>5785.99</v>
       </c>
       <c r="F17" t="n">
-        <v>65970.73</v>
+        <v>33891.74</v>
       </c>
       <c r="G17" t="n">
-        <v>16955.27</v>
+        <v>8296.9</v>
       </c>
       <c r="H17" t="n">
-        <v>2.93</v>
+        <v>1.43</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(16,955.27元)/活动清单.实际费用(5,785.99元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,296.90元)/活动清单.实际费用(5,785.99元)</t>
         </is>
       </c>
     </row>
@@ -1198,13 +1198,13 @@
         <v>14112.84</v>
       </c>
       <c r="F18" t="n">
-        <v>38056.68</v>
+        <v>52921.98</v>
       </c>
       <c r="G18" t="n">
-        <v>9240.82</v>
+        <v>13912.44</v>
       </c>
       <c r="H18" t="n">
-        <v>0.65</v>
+        <v>0.99</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(9,240.82元)/活动清单.实际费用(14,112.84元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(13,912.44元)/活动清单.实际费用(14,112.84元)</t>
         </is>
       </c>
     </row>
@@ -1242,22 +1242,22 @@
         <v>11836.73</v>
       </c>
       <c r="F19" t="n">
-        <v>58911.05</v>
+        <v>23062.09</v>
       </c>
       <c r="G19" t="n">
-        <v>20411.2</v>
+        <v>5909.88</v>
       </c>
       <c r="H19" t="n">
-        <v>1.72</v>
+        <v>0.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(20,411.20元)/活动清单.实际费用(11,836.73元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,909.88元)/活动清单.实际费用(11,836.73元)</t>
         </is>
       </c>
     </row>
@@ -1286,22 +1286,22 @@
         <v>2772.57</v>
       </c>
       <c r="F20" t="n">
-        <v>23732.33</v>
+        <v>42815.64</v>
       </c>
       <c r="G20" t="n">
-        <v>5337.47</v>
+        <v>10967.52</v>
       </c>
       <c r="H20" t="n">
-        <v>1.93</v>
+        <v>3.96</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,337.47元)/活动清单.实际费用(2,772.57元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,967.52元)/活动清单.实际费用(2,772.57元)</t>
         </is>
       </c>
     </row>
@@ -1330,22 +1330,22 @@
         <v>9135.48</v>
       </c>
       <c r="F21" t="n">
-        <v>69471.31</v>
+        <v>34611.99</v>
       </c>
       <c r="G21" t="n">
-        <v>15353.97</v>
+        <v>8105.06</v>
       </c>
       <c r="H21" t="n">
-        <v>1.68</v>
+        <v>0.89</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(15,353.97元)/活动清单.实际费用(9,135.48元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,105.06元)/活动清单.实际费用(9,135.48元)</t>
         </is>
       </c>
     </row>
@@ -1374,22 +1374,22 @@
         <v>3562.82</v>
       </c>
       <c r="F22" t="n">
-        <v>10113.4</v>
+        <v>16844.71</v>
       </c>
       <c r="G22" t="n">
-        <v>2159.61</v>
+        <v>4329.87</v>
       </c>
       <c r="H22" t="n">
-        <v>0.61</v>
+        <v>1.22</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(2,159.61元)/活动清单.实际费用(3,562.82元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,329.87元)/活动清单.实际费用(3,562.82元)</t>
         </is>
       </c>
     </row>
@@ -1418,22 +1418,22 @@
         <v>12365.5</v>
       </c>
       <c r="F23" t="n">
-        <v>100032.32</v>
+        <v>15213.67</v>
       </c>
       <c r="G23" t="n">
-        <v>18609.9</v>
+        <v>3930.63</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5</v>
+        <v>0.32</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(18,609.90元)/活动清单.实际费用(12,365.50元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(3,930.63元)/活动清单.实际费用(12,365.50元)</t>
         </is>
       </c>
     </row>
@@ -1462,22 +1462,22 @@
         <v>5533.43</v>
       </c>
       <c r="F24" t="n">
-        <v>103987.94</v>
+        <v>22792.09</v>
       </c>
       <c r="G24" t="n">
-        <v>21035.4</v>
+        <v>5752.65</v>
       </c>
       <c r="H24" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(21,035.40元)/活动清单.实际费用(5,533.43元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,752.65元)/活动清单.实际费用(5,533.43元)</t>
         </is>
       </c>
     </row>
@@ -1506,22 +1506,22 @@
         <v>11915.11</v>
       </c>
       <c r="F25" t="n">
-        <v>48203.7</v>
+        <v>88201.14999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>10723.09</v>
+        <v>25154.34</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9</v>
+        <v>2.11</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,723.09元)/活动清单.实际费用(11,915.11元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(25,154.34元)/活动清单.实际费用(11,915.11元)</t>
         </is>
       </c>
     </row>
@@ -1550,22 +1550,22 @@
         <v>7472.4</v>
       </c>
       <c r="F26" t="n">
-        <v>61560.37</v>
+        <v>20203.19</v>
       </c>
       <c r="G26" t="n">
-        <v>18574.61</v>
+        <v>5072.07</v>
       </c>
       <c r="H26" t="n">
-        <v>2.49</v>
+        <v>0.68</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(18,574.61元)/活动清单.实际费用(7,472.40元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,072.07元)/活动清单.实际费用(7,472.40元)</t>
         </is>
       </c>
     </row>
@@ -1594,13 +1594,13 @@
         <v>4473.51</v>
       </c>
       <c r="F27" t="n">
-        <v>77435.14</v>
+        <v>47626.75</v>
       </c>
       <c r="G27" t="n">
-        <v>12849.12</v>
+        <v>11738.31</v>
       </c>
       <c r="H27" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,849.12元)/活动清单.实际费用(4,473.51元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,738.31元)/活动清单.实际费用(4,473.51元)</t>
         </is>
       </c>
     </row>
@@ -1638,13 +1638,13 @@
         <v>11073.64</v>
       </c>
       <c r="F28" t="n">
-        <v>29592.1</v>
+        <v>34222.6</v>
       </c>
       <c r="G28" t="n">
-        <v>6346.7</v>
+        <v>9922.77</v>
       </c>
       <c r="H28" t="n">
-        <v>0.57</v>
+        <v>0.9</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(6,346.70元)/活动清单.实际费用(11,073.64元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(9,922.77元)/活动清单.实际费用(11,073.64元)</t>
         </is>
       </c>
     </row>
@@ -1682,22 +1682,22 @@
         <v>3594.29</v>
       </c>
       <c r="F29" t="n">
-        <v>29029.79</v>
+        <v>9202.75</v>
       </c>
       <c r="G29" t="n">
-        <v>7417.48</v>
+        <v>2482.03</v>
       </c>
       <c r="H29" t="n">
-        <v>2.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,417.48元)/活动清单.实际费用(3,594.29元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(2,482.03元)/活动清单.实际费用(3,594.29元)</t>
         </is>
       </c>
     </row>
@@ -1726,13 +1726,13 @@
         <v>5634.01</v>
       </c>
       <c r="F30" t="n">
-        <v>33794.86</v>
+        <v>43391.08</v>
       </c>
       <c r="G30" t="n">
-        <v>5849.08</v>
+        <v>11199.75</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,849.08元)/活动清单.实际费用(5,634.01元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,199.75元)/活动清单.实际费用(5,634.01元)</t>
         </is>
       </c>
     </row>
@@ -1770,22 +1770,22 @@
         <v>14470.09</v>
       </c>
       <c r="F31" t="n">
-        <v>92118.34</v>
+        <v>3508.07</v>
       </c>
       <c r="G31" t="n">
-        <v>19015.88</v>
+        <v>899.05</v>
       </c>
       <c r="H31" t="n">
-        <v>1.31</v>
+        <v>0.06</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(19,015.88元)/活动清单.实际费用(14,470.09元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(899.05元)/活动清单.实际费用(14,470.09元)</t>
         </is>
       </c>
     </row>
@@ -1814,13 +1814,13 @@
         <v>15528.58</v>
       </c>
       <c r="F32" t="n">
-        <v>9187.42</v>
+        <v>18515.28</v>
       </c>
       <c r="G32" t="n">
-        <v>2060.09</v>
+        <v>4798.99</v>
       </c>
       <c r="H32" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(2,060.09元)/活动清单.实际费用(15,528.58元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,798.99元)/活动清单.实际费用(15,528.58元)</t>
         </is>
       </c>
     </row>
@@ -1858,22 +1858,22 @@
         <v>13945.12</v>
       </c>
       <c r="F33" t="n">
-        <v>62844.73</v>
+        <v>107905.41</v>
       </c>
       <c r="G33" t="n">
-        <v>16447.27</v>
+        <v>27842.21</v>
       </c>
       <c r="H33" t="n">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>调整</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(16,447.27元)/活动清单.实际费用(13,945.12元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(27,842.21元)/活动清单.实际费用(13,945.12元)</t>
         </is>
       </c>
     </row>
@@ -1902,22 +1902,22 @@
         <v>11896.7</v>
       </c>
       <c r="F34" t="n">
-        <v>51697.07</v>
+        <v>79749.06</v>
       </c>
       <c r="G34" t="n">
-        <v>10837.62</v>
+        <v>19989.83</v>
       </c>
       <c r="H34" t="n">
-        <v>0.91</v>
+        <v>1.68</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,837.62元)/活动清单.实际费用(11,896.70元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(19,989.83元)/活动清单.实际费用(11,896.70元)</t>
         </is>
       </c>
     </row>
@@ -1946,22 +1946,22 @@
         <v>2890.2</v>
       </c>
       <c r="F35" t="n">
-        <v>66397.72</v>
+        <v>21456.4</v>
       </c>
       <c r="G35" t="n">
-        <v>17579.98</v>
+        <v>5579.8</v>
       </c>
       <c r="H35" t="n">
-        <v>6.08</v>
+        <v>1.93</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(17,579.98元)/活动清单.实际费用(2,890.20元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,579.80元)/活动清单.实际费用(2,890.20元)</t>
         </is>
       </c>
     </row>
@@ -1990,22 +1990,22 @@
         <v>3470.91</v>
       </c>
       <c r="F36" t="n">
-        <v>52765.84</v>
+        <v>2503.42</v>
       </c>
       <c r="G36" t="n">
-        <v>10511.97</v>
+        <v>606.38</v>
       </c>
       <c r="H36" t="n">
-        <v>3.03</v>
+        <v>0.17</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,511.97元)/活动清单.实际费用(3,470.91元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(606.38元)/活动清单.实际费用(3,470.91元)</t>
         </is>
       </c>
     </row>
@@ -2034,22 +2034,22 @@
         <v>11327.73</v>
       </c>
       <c r="F37" t="n">
-        <v>18315.89</v>
+        <v>48327.92</v>
       </c>
       <c r="G37" t="n">
-        <v>4552.04</v>
+        <v>14453.77</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4</v>
+        <v>1.28</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,552.04元)/活动清单.实际费用(11,327.73元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(14,453.77元)/活动清单.实际费用(11,327.73元)</t>
         </is>
       </c>
     </row>
@@ -2078,13 +2078,13 @@
         <v>8975.139999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>58272.9</v>
+        <v>47746.38</v>
       </c>
       <c r="G38" t="n">
-        <v>13616.56</v>
+        <v>12714.02</v>
       </c>
       <c r="H38" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(13,616.56元)/活动清单.实际费用(8,975.14元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,714.02元)/活动清单.实际费用(8,975.14元)</t>
         </is>
       </c>
     </row>
@@ -2122,22 +2122,22 @@
         <v>10473.02</v>
       </c>
       <c r="F39" t="n">
-        <v>29277.41</v>
+        <v>42636.83</v>
       </c>
       <c r="G39" t="n">
-        <v>8630.52</v>
+        <v>11044.25</v>
       </c>
       <c r="H39" t="n">
-        <v>0.82</v>
+        <v>1.05</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,630.52元)/活动清单.实际费用(10,473.02元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,044.25元)/活动清单.实际费用(10,473.02元)</t>
         </is>
       </c>
     </row>
@@ -2166,13 +2166,13 @@
         <v>4381.95</v>
       </c>
       <c r="F40" t="n">
-        <v>69534.55</v>
+        <v>63358.61</v>
       </c>
       <c r="G40" t="n">
-        <v>18424.66</v>
+        <v>17936</v>
       </c>
       <c r="H40" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(18,424.66元)/活动清单.实际费用(4,381.95元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(17,936.00元)/活动清单.实际费用(4,381.95元)</t>
         </is>
       </c>
     </row>
@@ -2210,13 +2210,13 @@
         <v>4119.28</v>
       </c>
       <c r="F41" t="n">
-        <v>69126.8</v>
+        <v>54056.29</v>
       </c>
       <c r="G41" t="n">
-        <v>12085.1</v>
+        <v>13531.15</v>
       </c>
       <c r="H41" t="n">
-        <v>2.93</v>
+        <v>3.28</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,085.10元)/活动清单.实际费用(4,119.28元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(13,531.15元)/活动清单.实际费用(4,119.28元)</t>
         </is>
       </c>
     </row>
@@ -2254,22 +2254,22 @@
         <v>2110.03</v>
       </c>
       <c r="F42" t="n">
-        <v>56140.97</v>
+        <v>10132.89</v>
       </c>
       <c r="G42" t="n">
-        <v>12012.59</v>
+        <v>2634.14</v>
       </c>
       <c r="H42" t="n">
-        <v>5.69</v>
+        <v>1.25</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,012.59元)/活动清单.实际费用(2,110.03元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(2,634.14元)/活动清单.实际费用(2,110.03元)</t>
         </is>
       </c>
     </row>
@@ -2298,13 +2298,13 @@
         <v>11099.07</v>
       </c>
       <c r="F43" t="n">
-        <v>47517.01</v>
+        <v>30366.96</v>
       </c>
       <c r="G43" t="n">
-        <v>10717.52</v>
+        <v>7955.08</v>
       </c>
       <c r="H43" t="n">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,717.52元)/活动清单.实际费用(11,099.07元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,955.08元)/活动清单.实际费用(11,099.07元)</t>
         </is>
       </c>
     </row>
@@ -2342,13 +2342,13 @@
         <v>14244.19</v>
       </c>
       <c r="F44" t="n">
-        <v>31001.77</v>
+        <v>30260.3</v>
       </c>
       <c r="G44" t="n">
-        <v>6119.49</v>
+        <v>7520.54</v>
       </c>
       <c r="H44" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(6,119.49元)/活动清单.实际费用(14,244.19元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,520.54元)/活动清单.实际费用(14,244.19元)</t>
         </is>
       </c>
     </row>
@@ -2386,22 +2386,22 @@
         <v>12714.32</v>
       </c>
       <c r="F45" t="n">
-        <v>14419.92</v>
+        <v>51928.97</v>
       </c>
       <c r="G45" t="n">
-        <v>2148.36</v>
+        <v>13631.51</v>
       </c>
       <c r="H45" t="n">
-        <v>0.17</v>
+        <v>1.07</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>调整</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(2,148.36元)/活动清单.实际费用(12,714.32元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(13,631.51元)/活动清单.实际费用(12,714.32元)</t>
         </is>
       </c>
     </row>
@@ -2430,13 +2430,13 @@
         <v>14090.22</v>
       </c>
       <c r="F46" t="n">
-        <v>34575.88</v>
+        <v>32357.74</v>
       </c>
       <c r="G46" t="n">
-        <v>6639.58</v>
+        <v>9043.24</v>
       </c>
       <c r="H46" t="n">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(6,639.58元)/活动清单.实际费用(14,090.22元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(9,043.24元)/活动清单.实际费用(14,090.22元)</t>
         </is>
       </c>
     </row>
@@ -2474,13 +2474,13 @@
         <v>6567.16</v>
       </c>
       <c r="F47" t="n">
-        <v>68031.12</v>
+        <v>39146.55</v>
       </c>
       <c r="G47" t="n">
-        <v>11637.05</v>
+        <v>10518.88</v>
       </c>
       <c r="H47" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,637.05元)/活动清单.实际费用(6,567.16元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,518.88元)/活动清单.实际费用(6,567.16元)</t>
         </is>
       </c>
     </row>
@@ -2518,13 +2518,13 @@
         <v>11791.47</v>
       </c>
       <c r="F48" t="n">
-        <v>25553.34</v>
+        <v>43783.17</v>
       </c>
       <c r="G48" t="n">
-        <v>6082.83</v>
+        <v>11346.02</v>
       </c>
       <c r="H48" t="n">
-        <v>0.52</v>
+        <v>0.96</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(6,082.83元)/活动清单.实际费用(11,791.47元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,346.02元)/活动清单.实际费用(11,791.47元)</t>
         </is>
       </c>
     </row>
@@ -2562,13 +2562,13 @@
         <v>13348.43</v>
       </c>
       <c r="F49" t="n">
-        <v>40545.47</v>
+        <v>5742.98</v>
       </c>
       <c r="G49" t="n">
-        <v>9090.17</v>
+        <v>1257.08</v>
       </c>
       <c r="H49" t="n">
-        <v>0.68</v>
+        <v>0.09</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(9,090.17元)/活动清单.实际费用(13,348.43元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(1,257.08元)/活动清单.实际费用(13,348.43元)</t>
         </is>
       </c>
     </row>
@@ -2606,22 +2606,22 @@
         <v>3888.45</v>
       </c>
       <c r="F50" t="n">
-        <v>15314.82</v>
+        <v>40241.31</v>
       </c>
       <c r="G50" t="n">
-        <v>3112.38</v>
+        <v>11350.5</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8</v>
+        <v>2.92</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>保留</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(3,112.38元)/活动清单.实际费用(3,888.45元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,350.50元)/活动清单.实际费用(3,888.45元)</t>
         </is>
       </c>
     </row>
@@ -2650,22 +2650,22 @@
         <v>12873.49</v>
       </c>
       <c r="F51" t="n">
-        <v>118190.11</v>
+        <v>19870.39</v>
       </c>
       <c r="G51" t="n">
-        <v>28883.19</v>
+        <v>4953.05</v>
       </c>
       <c r="H51" t="n">
-        <v>2.24</v>
+        <v>0.38</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>保留</t>
+          <t>取消</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(28,883.19元)/活动清单.实际费用(12,873.49元)</t>
+          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,953.05元)/活动清单.实际费用(12,873.49元)</t>
         </is>
       </c>
     </row>

--- a/output/促销组合优化建议.xlsx
+++ b/output/促销组合优化建议.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活动评估" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H2节奏建议" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,13 +27,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,8 +56,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2670,6 +2687,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="I2:I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+      <formula1>"保留,调整,取消"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2840,4 +2862,111 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>活动评估 自查区(只读;公式由 Excel 计算)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>校验项</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>期望/口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>活动行数</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>COUNTA('活动评估'!A2:A51)</f>
+        <v/>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>应为 50(全量活动)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ROI 最大差异(按呈现精度比对)</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>MAX(ABS('活动评估'!H2:H51-ROUND('活动评估'!G2:G51/'活动评估'!E2:E51,2)))</f>
+        <v/>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>ROI = 增量毛利 ÷ 实际费用,按 2 位小数呈现后比对;应 ≤ 0.0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>枚举违规行数(建议动作)</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUMPRODUCT(--(ISNA(MATCH('活动评估'!I2:I51,{"保留";"调整";"取消"},0))))</f>
+        <v/>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>建议动作取值应落在规定集合内;应为 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>H2 节奏建议月份数</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>COUNTA('H2节奏建议'!A2:A7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>应为 6(2026-07 ~ 2026-12)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/促销组合优化建议.xlsx
+++ b/output/促销组合优化建议.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活动评估" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H2节奏建议" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H2 节奏建议" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>

--- a/output/促销组合优化建议.xlsx
+++ b/output/促销组合优化建议.xlsx
@@ -2688,7 +2688,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
+    <dataValidation sqref="I2:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值超出规定枚举" error="请使用规定枚举值" type="list">
       <formula1>"保留,调整,取消"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/促销组合优化建议.xlsx
+++ b/output/促销组合优化建议.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活动评估" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="H2 节奏建议" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,21 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,16 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2862,111 +2845,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>活动评估 自查区(只读;公式由 Excel 计算)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>校验项</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>结果</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>期望/口径</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>活动行数</t>
-        </is>
-      </c>
-      <c r="B4" s="3">
-        <f>COUNTA('活动评估'!A2:A51)</f>
-        <v/>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>应为 50(全量活动)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ROI 最大差异(按呈现精度比对)</t>
-        </is>
-      </c>
-      <c r="B5" s="3">
-        <f>MAX(ABS('活动评估'!H2:H51-ROUND('活动评估'!G2:G51/'活动评估'!E2:E51,2)))</f>
-        <v/>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>ROI = 增量毛利 ÷ 实际费用,按 2 位小数呈现后比对;应 ≤ 0.0005</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>枚举违规行数(建议动作)</t>
-        </is>
-      </c>
-      <c r="B6" s="3">
-        <f>SUMPRODUCT(--(ISNA(MATCH('活动评估'!I2:I51,{"保留";"调整";"取消"},0))))</f>
-        <v/>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>建议动作取值应落在规定集合内;应为 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>H2 节奏建议月份数</t>
-        </is>
-      </c>
-      <c r="B7" s="3">
-        <f>COUNTA('H2节奏建议'!A2:A7)</f>
-        <v/>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>应为 6(2026-07 ~ 2026-12)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/促销组合优化建议.xlsx
+++ b/output/促销组合优化建议.xlsx
@@ -435,22 +435,22 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>渠道ID</t>
+          <t>渠道</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>实际费用(元)</t>
+          <t>实际费用</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>增量销售额(元)</t>
+          <t>增量销售额</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>增量毛利(元)</t>
+          <t>增量毛利</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -460,7 +460,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>建议动作</t>
+          <t>建议动作(保留/调整/取消)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,593.91元)/活动清单.实际费用(6,741.41元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(11,593.91 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(6,741.41 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,754.44元)/活动清单.实际费用(6,968.65元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(4,754.44 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(6,968.65 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(16,465.53元)/活动清单.实际费用(6,109.20元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(16,465.53 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(6,109.20 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,358.97元)/活动清单.实际费用(6,556.05元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(8,358.97 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(6,556.05 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,181.90元)/活动清单.实际费用(4,640.84元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(11,181.90 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(4,640.84 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,973.69元)/活动清单.实际费用(10,630.78元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(7,973.69 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(10,630.78 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,097.34元)/活动清单.实际费用(14,866.74元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(5,097.34 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(14,866.74 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(15,250.31元)/活动清单.实际费用(7,520.83元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(15,250.31 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(7,520.83 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,845.56元)/活动清单.实际费用(3,337.67元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(8,845.56 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(3,337.67 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,352.85元)/活动清单.实际费用(5,419.13元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(12,352.85 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(5,419.13 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,516.62元)/活动清单.实际费用(5,952.00元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(7,516.62 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(5,952.00 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(3,411.63元)/活动清单.实际费用(4,666.14元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(3,411.63 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(4,666.14 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,465.44元)/活动清单.实际费用(3,457.45元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(4,465.44 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(3,457.45 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(13,178.84元)/活动清单.实际费用(6,394.80元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(13,178.84 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(6,394.80 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(27,043.37元)/活动清单.实际费用(9,459.97元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(27,043.37 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(9,459.97 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,296.90元)/活动清单.实际费用(5,785.99元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(8,296.90 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(5,785.99 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(13,912.44元)/活动清单.实际费用(14,112.84元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(13,912.44 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(14,112.84 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,909.88元)/活动清单.实际费用(11,836.73元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(5,909.88 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(11,836.73 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,967.52元)/活动清单.实际费用(2,772.57元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(10,967.52 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(2,772.57 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(8,105.06元)/活动清单.实际费用(9,135.48元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(8,105.06 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(9,135.48 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,329.87元)/活动清单.实际费用(3,562.82元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(4,329.87 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(3,562.82 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(3,930.63元)/活动清单.实际费用(12,365.50元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(3,930.63 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(12,365.50 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,752.65元)/活动清单.实际费用(5,533.43元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(5,752.65 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(5,533.43 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(25,154.34元)/活动清单.实际费用(11,915.11元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(25,154.34 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(11,915.11 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,072.07元)/活动清单.实际费用(7,472.40元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(5,072.07 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(7,472.40 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,738.31元)/活动清单.实际费用(4,473.51元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(11,738.31 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(4,473.51 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(9,922.77元)/活动清单.实际费用(11,073.64元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(9,922.77 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(11,073.64 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(2,482.03元)/活动清单.实际费用(3,594.29元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(2,482.03 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(3,594.29 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,199.75元)/活动清单.实际费用(5,634.01元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(11,199.75 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(5,634.01 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(899.05元)/活动清单.实际费用(14,470.09元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(899.05 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(14,470.09 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,798.99元)/活动清单.实际费用(15,528.58元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(4,798.99 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(15,528.58 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(27,842.21元)/活动清单.实际费用(13,945.12元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(27,842.21 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(13,945.12 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(19,989.83元)/活动清单.实际费用(11,896.70元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(19,989.83 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(11,896.70 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(5,579.80元)/活动清单.实际费用(2,890.20元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(5,579.80 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(2,890.20 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(606.38元)/活动清单.实际费用(3,470.91元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(606.38 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(3,470.91 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(14,453.77元)/活动清单.实际费用(11,327.73元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(14,453.77 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(11,327.73 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(12,714.02元)/活动清单.实际费用(8,975.14元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(12,714.02 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(8,975.14 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,044.25元)/活动清单.实际费用(10,473.02元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(11,044.25 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(10,473.02 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(17,936.00元)/活动清单.实际费用(4,381.95元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(17,936.00 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(4,381.95 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(13,531.15元)/活动清单.实际费用(4,119.28元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(13,531.15 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(4,119.28 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(2,634.14元)/活动清单.实际费用(2,110.03元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(2,634.14 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(2,110.03 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,955.08元)/活动清单.实际费用(11,099.07元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(7,955.08 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(11,099.07 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(7,520.54元)/活动清单.实际费用(14,244.19元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(7,520.54 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(14,244.19 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(13,631.51元)/活动清单.实际费用(12,714.32元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(13,631.51 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(12,714.32 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(9,043.24元)/活动清单.实际费用(14,090.22元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(9,043.24 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(14,090.22 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(10,518.88元)/活动清单.实际费用(6,567.16元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(10,518.88 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(6,567.16 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,346.02元)/活动清单.实际费用(11,791.47元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(11,346.02 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(11,791.47 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(1,257.08元)/活动清单.实际费用(13,348.43元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(1,257.08 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(13,348.43 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(11,350.50元)/活动清单.实际费用(3,888.45元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(11,350.50 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(3,888.45 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>《2026H1促销活动记录.xlsx》活动效果.增量毛利(4,953.05元)/活动清单.实际费用(12,873.49元)</t>
+          <t>《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利`(4,953.05 元);《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`(12,873.49 元);ROI = 《2026H1促销活动记录.xlsx》Sheet「活动效果」的 `增量毛利` ÷ 《2026H1促销活动记录.xlsx》Sheet「活动清单」的 `实际费用`</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>预算区间(元)</t>
+          <t>预算区间</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
